--- a/doc/Микросхемы_цены.xlsx
+++ b/doc/Микросхемы_цены.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My\HomePC\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E83C439-A3AD-43BF-9107-02FBE6767114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09F05B5-50B4-4BB3-9E36-3A50CD01BBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="5550" windowWidth="19170" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
   <si>
     <t>К155ТМ2</t>
   </si>
@@ -265,6 +268,12 @@
   </si>
   <si>
     <t>К155ИР13</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -804,7 +813,9 @@
         <v>3</v>
       </c>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11" s="11"/>
@@ -945,6 +956,9 @@
       <c r="B20" s="8">
         <v>2</v>
       </c>
+      <c r="D20" s="8">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -953,6 +967,9 @@
       <c r="B21" s="8">
         <v>4</v>
       </c>
+      <c r="D21" s="8">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -961,6 +978,9 @@
       <c r="B22" s="8">
         <v>11</v>
       </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -969,6 +989,9 @@
       <c r="B23" s="8">
         <v>3</v>
       </c>
+      <c r="D23">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -988,6 +1011,9 @@
       <c r="B25" s="8">
         <v>3</v>
       </c>
+      <c r="D25">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -996,6 +1022,9 @@
       <c r="B26" s="8">
         <v>2</v>
       </c>
+      <c r="D26">
+        <v>0.28999999999999998</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1004,6 +1033,9 @@
       <c r="B27" s="8">
         <v>3</v>
       </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -1024,6 +1056,9 @@
       <c r="B29" s="8">
         <v>2</v>
       </c>
+      <c r="D29">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1032,6 +1067,9 @@
       <c r="B30" s="8">
         <v>2</v>
       </c>
+      <c r="D30">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1040,6 +1078,9 @@
       <c r="B31" s="8">
         <v>2</v>
       </c>
+      <c r="D31">
+        <v>1.26</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1059,6 +1100,9 @@
       <c r="B33" s="8">
         <v>1</v>
       </c>
+      <c r="D33">
+        <v>0.57999999999999996</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -1067,6 +1111,9 @@
       <c r="B34" s="8">
         <v>4</v>
       </c>
+      <c r="D34">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1075,6 +1122,9 @@
       <c r="B35" s="8">
         <v>6</v>
       </c>
+      <c r="D35" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1083,6 +1133,9 @@
       <c r="B36" s="8">
         <v>4</v>
       </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1091,6 +1144,9 @@
       <c r="B37" s="8">
         <v>1</v>
       </c>
+      <c r="D37">
+        <v>2.92</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1099,6 +1155,9 @@
       <c r="B38" s="8">
         <v>4</v>
       </c>
+      <c r="D38">
+        <v>4.67</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1107,6 +1166,9 @@
       <c r="B39" s="8">
         <v>2</v>
       </c>
+      <c r="D39">
+        <v>0.28999999999999998</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1115,6 +1177,9 @@
       <c r="B40" s="8">
         <v>4</v>
       </c>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -1123,6 +1188,9 @@
       <c r="B41" s="8">
         <v>2</v>
       </c>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -1153,6 +1221,9 @@
       <c r="B44" s="8">
         <v>1</v>
       </c>
+      <c r="D44">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1183,6 +1254,9 @@
       <c r="B47">
         <v>3</v>
       </c>
+      <c r="D47">
+        <v>7.01</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1191,45 +1265,63 @@
       <c r="B48">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>75</v>
       </c>
       <c r="B49">
         <v>9</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>76</v>
       </c>
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
       <c r="B51">
         <v>63</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
       <c r="B52">
         <v>9</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>78</v>
       </c>
       <c r="B53">
         <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
